--- a/cet4/result/19_重生影后_舞台上的女王/19_重生影后_舞台上的女王_学习版.xlsx
+++ b/cet4/result/19_重生影后_舞台上的女王/19_重生影后_舞台上的女王_学习版.xlsx
@@ -397,801 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>August</v>
       </c>
       <c r="B2" t="str">
-        <v>August</v>
+        <v>/ɔːˈɡʌst/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>八月</v>
       </c>
-      <c r="D2" t="str">
-        <v>August(八月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>avenue</v>
       </c>
       <c r="B3" t="str">
-        <v>avenue</v>
+        <v>/ˈævənuː/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>大街</v>
       </c>
-      <c r="D3" t="str">
-        <v>avenue(大街)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>unique</v>
       </c>
       <c r="B4" t="str">
-        <v>unique</v>
+        <v>/juˈniːk/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>独特的</v>
       </c>
-      <c r="D4" t="str">
-        <v>unique(独特的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>eleventh</v>
       </c>
       <c r="B5" t="str">
-        <v>eleventh</v>
+        <v>/ɪˈlevnθ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D5" t="str">
         <v>第十一</v>
       </c>
-      <c r="D5" t="str">
-        <v>eleventh(第十一)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>advance</v>
       </c>
       <c r="B6" t="str">
-        <v>advance</v>
+        <v>/ədˈvæns/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>前进</v>
       </c>
-      <c r="D6" t="str">
-        <v>advance(前进)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>obstacle</v>
       </c>
       <c r="B7" t="str">
-        <v>obstacle</v>
+        <v>/ˈɑːbstəkl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>障碍</v>
       </c>
-      <c r="D7" t="str">
-        <v>obstacle(障碍)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>practical</v>
       </c>
       <c r="B8" t="str">
-        <v>practical</v>
+        <v>/ˈpræktɪkl/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>实际的</v>
       </c>
-      <c r="D8" t="str">
-        <v>practical(实际的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>meadow</v>
       </c>
       <c r="B9" t="str">
-        <v>meadow</v>
+        <v>/ˈmedoʊ/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>草地</v>
       </c>
-      <c r="D9" t="str">
-        <v>meadow(草地)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>ray</v>
       </c>
       <c r="B10" t="str">
-        <v>ray</v>
+        <v>/reɪ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>光线</v>
       </c>
-      <c r="D10" t="str">
-        <v>ray(光线)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>stretch</v>
       </c>
       <c r="B11" t="str">
-        <v>stretch</v>
+        <v>/stretʃ/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>伸展</v>
       </c>
-      <c r="D11" t="str">
-        <v>stretch(伸展)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>representative</v>
       </c>
       <c r="B12" t="str">
-        <v>representative</v>
+        <v>/ˌreprɪˈzentətɪv/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>代表</v>
       </c>
-      <c r="D12" t="str">
-        <v>representative(代表)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>information</v>
       </c>
       <c r="B13" t="str">
-        <v>information</v>
+        <v>/ˌɪnfərˈmeɪʃn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>信息</v>
       </c>
-      <c r="D13" t="str">
-        <v>information(信息)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>soon</v>
       </c>
       <c r="B14" t="str">
-        <v>soon</v>
+        <v>/suːn/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>很快</v>
       </c>
-      <c r="D14" t="str">
-        <v>soon(很快)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>Spanish</v>
       </c>
       <c r="B15" t="str">
-        <v>Spanish</v>
+        <v>/ˈspænɪʃ/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>西班牙的</v>
       </c>
-      <c r="D15" t="str">
-        <v>Spanish(西班牙的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>dish</v>
       </c>
       <c r="B16" t="str">
-        <v>dish</v>
+        <v>/dɪʃ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>盘子</v>
       </c>
-      <c r="D16" t="str">
-        <v>dish(盘子)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>phrase</v>
       </c>
       <c r="B17" t="str">
-        <v>phrase</v>
+        <v>/freɪz/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D17" t="str">
         <v>短语</v>
       </c>
-      <c r="D17" t="str">
-        <v>phrase(短语)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>refer</v>
       </c>
       <c r="B18" t="str">
-        <v>refer</v>
+        <v>/rɪˈfɜːr/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>参考</v>
       </c>
-      <c r="D18" t="str">
-        <v>refer(参考)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>pride</v>
       </c>
       <c r="B19" t="str">
-        <v>pride</v>
+        <v>/praɪd/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>自豪</v>
       </c>
-      <c r="D19" t="str">
-        <v>pride(自豪)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>five</v>
       </c>
       <c r="B20" t="str">
-        <v>five</v>
+        <v>/faɪv/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D20" t="str">
         <v>五</v>
       </c>
-      <c r="D20" t="str">
-        <v>five(五)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>ton</v>
       </c>
       <c r="B21" t="str">
-        <v>ton</v>
+        <v>/tʌn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>吨</v>
       </c>
-      <c r="D21" t="str">
-        <v>ton(吨)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>above</v>
       </c>
       <c r="B22" t="str">
-        <v>above</v>
+        <v>/əˈbʌv/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adj./adv./prep.</v>
+      </c>
+      <c r="D22" t="str">
         <v>在上方</v>
       </c>
-      <c r="D22" t="str">
-        <v>above(在上方)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>incorrect</v>
       </c>
       <c r="B23" t="str">
-        <v>incorrect</v>
+        <v>/ˌɪnkəˈrekt/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>错误的</v>
       </c>
-      <c r="D23" t="str">
-        <v>incorrect(错误的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>nasty</v>
       </c>
       <c r="B24" t="str">
-        <v>practical</v>
+        <v>/ˈnæsti/</v>
       </c>
       <c r="C24" t="str">
-        <v>实际的</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>practical(实际的)📢</v>
+        <v>讨厌的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>despise</v>
       </c>
       <c r="B25" t="str">
-        <v>nasty</v>
+        <v>/dɪˈspaɪz/</v>
       </c>
       <c r="C25" t="str">
-        <v>讨厌的</v>
+        <v>vt.</v>
       </c>
       <c r="D25" t="str">
-        <v>nasty(讨厌的)📢</v>
+        <v>轻视</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>beyond</v>
       </c>
       <c r="B26" t="str">
-        <v>despise</v>
+        <v>/bɪˈjɑːnd/</v>
       </c>
       <c r="C26" t="str">
-        <v>轻视</v>
+        <v>n./v./adv./prep.</v>
       </c>
       <c r="D26" t="str">
-        <v>despise(轻视)📢</v>
+        <v>超过</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>steward</v>
       </c>
       <c r="B27" t="str">
-        <v>soon</v>
+        <v>/ˈstuːərd/</v>
       </c>
       <c r="C27" t="str">
-        <v>很快</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>soon(很快)📢</v>
+        <v>乘务员</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>respectively</v>
       </c>
       <c r="B28" t="str">
-        <v>beyond</v>
+        <v>/rɪˈspektɪvli/</v>
       </c>
       <c r="C28" t="str">
-        <v>超过</v>
+        <v>v./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>beyond(超过)📢</v>
+        <v>分别地</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>explosive</v>
       </c>
       <c r="B29" t="str">
-        <v>steward</v>
+        <v>/ɪkˈspləʊsɪv/</v>
       </c>
       <c r="C29" t="str">
-        <v>乘务员</v>
+        <v>n./adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>steward(乘务员)📢</v>
+        <v>爆炸性的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>goodness</v>
       </c>
       <c r="B30" t="str">
-        <v>respectively</v>
+        <v>/ˈɡʊdnəs/</v>
       </c>
       <c r="C30" t="str">
-        <v>分别地</v>
+        <v>n./int.</v>
       </c>
       <c r="D30" t="str">
-        <v>respectively(分别地)📢</v>
+        <v>善良</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>consist</v>
       </c>
       <c r="B31" t="str">
-        <v>above</v>
+        <v>/kənˈsɪst/</v>
       </c>
       <c r="C31" t="str">
-        <v>在上方</v>
+        <v>vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>above(在上方)📢</v>
+        <v>由...组成</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>reflect</v>
       </c>
       <c r="B32" t="str">
-        <v>explosive</v>
+        <v>/rɪˈflekt/</v>
       </c>
       <c r="C32" t="str">
-        <v>爆炸性的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>explosive(爆炸性的)📢</v>
+        <v>反映</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>come</v>
       </c>
       <c r="B33" t="str">
-        <v>goodness</v>
+        <v>/kʌm/</v>
       </c>
       <c r="C33" t="str">
-        <v>善良</v>
+        <v>n./vt./vi./int.</v>
       </c>
       <c r="D33" t="str">
-        <v>goodness(善良)📢</v>
+        <v>来</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>commerce</v>
       </c>
       <c r="B34" t="str">
-        <v>consist</v>
+        <v>/ˈkɑːmɜːrs/</v>
       </c>
       <c r="C34" t="str">
-        <v>由...组成</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>consist(由...组成)📢</v>
+        <v>商业</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>settlement</v>
       </c>
       <c r="B35" t="str">
-        <v>reflect</v>
+        <v>/ˈsetlmənt/</v>
       </c>
       <c r="C35" t="str">
-        <v>反映</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>reflect(反映)📢</v>
+        <v>解决</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>link</v>
       </c>
       <c r="B36" t="str">
-        <v>come</v>
+        <v>/lɪŋk/</v>
       </c>
       <c r="C36" t="str">
-        <v>来</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>come(来)📢</v>
+        <v>连接</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>range</v>
       </c>
       <c r="B37" t="str">
-        <v>commerce</v>
+        <v>/reɪndʒ/</v>
       </c>
       <c r="C37" t="str">
-        <v>商业</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>commerce(商业)📢</v>
+        <v>范围</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>restore</v>
       </c>
       <c r="B38" t="str">
-        <v>settlement</v>
+        <v>/rɪˈstɔːr/</v>
       </c>
       <c r="C38" t="str">
-        <v>解决</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>settlement(解决)📢</v>
+        <v>恢复</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>storm</v>
       </c>
       <c r="B39" t="str">
-        <v>link</v>
+        <v>/stɔːrm/</v>
       </c>
       <c r="C39" t="str">
-        <v>连接</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>link(连接)📢</v>
+        <v>暴风雨</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>headline</v>
       </c>
       <c r="B40" t="str">
-        <v>range</v>
+        <v>/ˈhedlaɪn/</v>
       </c>
       <c r="C40" t="str">
-        <v>范围</v>
+        <v>n./vt.</v>
       </c>
       <c r="D40" t="str">
-        <v>range(范围)📢</v>
+        <v>标题</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>protect</v>
       </c>
       <c r="B41" t="str">
-        <v>restore</v>
+        <v>/prəˈtekt/</v>
       </c>
       <c r="C41" t="str">
-        <v>恢复</v>
+        <v>vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>restore(恢复)📢</v>
+        <v>保护</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>benefit</v>
       </c>
       <c r="B42" t="str">
-        <v>storm</v>
+        <v>/ˈbenɪfɪt/</v>
       </c>
       <c r="C42" t="str">
-        <v>暴风雨</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>storm(暴风雨)📢</v>
+        <v>利益</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>shady</v>
       </c>
       <c r="B43" t="str">
-        <v>headline</v>
+        <v>/ˈʃeɪdi/</v>
       </c>
       <c r="C43" t="str">
-        <v>标题</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>headline(标题)📢</v>
+        <v>阴暗的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>viewpoint</v>
       </c>
       <c r="B44" t="str">
-        <v>pride</v>
+        <v>/ˈvjuːpɔɪnt/</v>
       </c>
       <c r="C44" t="str">
-        <v>自豪</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>pride(自豪)📢</v>
+        <v>观点</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>whirl</v>
       </c>
       <c r="B45" t="str">
-        <v>protect</v>
+        <v>/wɜːrl/</v>
       </c>
       <c r="C45" t="str">
-        <v>保护</v>
+        <v>n./v.</v>
       </c>
       <c r="D45" t="str">
-        <v>protect(保护)📢</v>
+        <v>旋转</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>pinch</v>
       </c>
       <c r="B46" t="str">
-        <v>benefit</v>
+        <v>/pɪntʃ/</v>
       </c>
       <c r="C46" t="str">
-        <v>利益</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>benefit(利益)📢</v>
+        <v>捏</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>infect</v>
       </c>
       <c r="B47" t="str">
-        <v>reflect</v>
+        <v>/ɪnˈfekt/</v>
       </c>
       <c r="C47" t="str">
-        <v>反映</v>
+        <v>vt.</v>
       </c>
       <c r="D47" t="str">
-        <v>reflect(反映)📢</v>
+        <v>感染</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>reflection</v>
       </c>
       <c r="B48" t="str">
-        <v>shady</v>
+        <v>/rɪˈflekʃn/</v>
       </c>
       <c r="C48" t="str">
-        <v>阴暗的</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>shady(阴暗的)📢</v>
+        <v>反射</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>assist</v>
       </c>
       <c r="B49" t="str">
-        <v>despise</v>
+        <v>/əˈsɪst/</v>
       </c>
       <c r="C49" t="str">
-        <v>轻视</v>
+        <v>v.</v>
       </c>
       <c r="D49" t="str">
-        <v>despise(轻视)📢</v>
+        <v>帮助</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>absence</v>
       </c>
       <c r="B50" t="str">
-        <v>viewpoint</v>
+        <v>/ˈæbsəns/</v>
       </c>
       <c r="C50" t="str">
-        <v>观点</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>viewpoint(观点)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>whirl</v>
-      </c>
-      <c r="C51" t="str">
-        <v>旋转</v>
-      </c>
-      <c r="D51" t="str">
-        <v>whirl(旋转)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>pinch</v>
-      </c>
-      <c r="C52" t="str">
-        <v>捏</v>
-      </c>
-      <c r="D52" t="str">
-        <v>pinch(捏)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>infect</v>
-      </c>
-      <c r="C53" t="str">
-        <v>感染</v>
-      </c>
-      <c r="D53" t="str">
-        <v>infect(感染)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>reflection</v>
-      </c>
-      <c r="C54" t="str">
-        <v>反射</v>
-      </c>
-      <c r="D54" t="str">
-        <v>reflection(反射)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>assist</v>
-      </c>
-      <c r="C55" t="str">
-        <v>帮助</v>
-      </c>
-      <c r="D55" t="str">
-        <v>assist(帮助)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>absence</v>
-      </c>
-      <c r="C56" t="str">
         <v>缺席</v>
-      </c>
-      <c r="D56" t="str">
-        <v>absence(缺席)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>